--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>המשקפיים של נויפלד עם יהורם גאון – בינתיים</v>
+        <v>הראל מויאל – חי באנשים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-15</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%9e%d7%a9%d7%a7%d7%a4%d7%99%d7%99%d7%9d-%d7%a9%d7%9c-%d7%a0%d7%95%d7%99%d7%a4%d7%9c%d7%93-%d7%a2%d7%9d-%d7%99%d7%94%d7%95%d7%a8%d7%9d-%d7%92%d7%90%d7%95%d7%9f-%d7%91%d7%99%d7%a0%d7%aa%d7%99/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a8%d7%90%d7%9c-%d7%9e%d7%95%d7%99%d7%90%d7%9c-%d7%97%d7%99-%d7%91%d7%90%d7%a0%d7%a9%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-15</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "בינתיים” בביצועו של יהורם גאון שמשתלב בפרויקט של שמוליק נויפלד נסב סביב רעיון ה״בינתיים״ – אותה תחושת השהיה קיומית, בין עבר טעון לעתיד לא ברור. אבל דווקא בתוך המסגרת הזו, זה אינו שיר פסימי, אלא שיר אהבה מפוכח,  נאמן.</v>
+        <v>השיר "חי באנשים” (***) בביצועו של הראל מויאל מצטרף למסורת ארוכה של שירי זיכרון , אך מביא איתו גישה מעט שונה: פחות קינה ישירה, ויותר ניסיון לעבד את האובדן דרך המשכיות, נוכחות וזיכרון חי. הטקסט מגדיר את הנרטיב לא כשיר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>המשקפיים של נויפלד עם יהורם גאון – בינתיים</v>
+        <v>הראל מויאל – חי באנשים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הראל מויאל – חי באנשים</v>
+        <v>דודי בר דוד – כל ההכי טובים</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a8%d7%90%d7%9c-%d7%9e%d7%95%d7%99%d7%90%d7%9c-%d7%97%d7%99-%d7%91%d7%90%d7%a0%d7%a9%d7%99%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%93%d7%99-%d7%91%d7%a8-%d7%93%d7%95%d7%93-%d7%9b%d7%9c-%d7%94%d7%94%d7%9b%d7%99-%d7%98%d7%95%d7%91%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "חי באנשים” (***) בביצועו של הראל מויאל מצטרף למסורת ארוכה של שירי זיכרון , אך מביא איתו גישה מעט שונה: פחות קינה ישירה, ויותר ניסיון לעבד את האובדן דרך המשכיות, נוכחות וזיכרון חי. הטקסט מגדיר את הנרטיב לא כשיר</v>
+        <v>השיר "כל ההכי טובים” של דודי בר דוד הוא שיר זיכרון שמסרב להיות “שיר זיכרון” במובן המוכר. במקום טקסטים נשגבים או מטאפורות גדולות – הוא בוחר בפרטים הקטנים, היומיומיים, כמעט האפורים. דווקא שם נמצא הכאב. כבר בשורות הראשונות: “קוראת תהילים</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הראל מויאל – חי באנשים</v>
+        <v>דודי בר דוד – כל ההכי טובים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>דודי בר דוד – כל ההכי טובים</v>
+        <v>מיכל גרינגליק – לוח זכרונות</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%93%d7%99-%d7%91%d7%a8-%d7%93%d7%95%d7%93-%d7%9b%d7%9c-%d7%94%d7%94%d7%9b%d7%99-%d7%98%d7%95%d7%91%d7%99%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%9b%d7%9c-%d7%92%d7%a8%d7%99%d7%a0%d7%92%d7%9c%d7%99%d7%a7-%d7%9c%d7%95%d7%97-%d7%96%d7%9b%d7%a8%d7%95%d7%a0%d7%95%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "כל ההכי טובים” של דודי בר דוד הוא שיר זיכרון שמסרב להיות “שיר זיכרון” במובן המוכר. במקום טקסטים נשגבים או מטאפורות גדולות – הוא בוחר בפרטים הקטנים, היומיומיים, כמעט האפורים. דווקא שם נמצא הכאב. כבר בשורות הראשונות: “קוראת תהילים</v>
+        <v>השיר "לוח זכרונות" של מיכל גרינגליק מציג חוויה מאוד אישית של אבל בתוך מסגרת קולקטיבית של יום הזיכרון לחללי צה"ל. זה שיר שלא רק מתאר כאב – הוא  מתנהל בתוך הכאב, תוך ניסיון כושל (ומודע לעצמו) לעבד אותו דרך מוזיקה.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>דודי בר דוד – כל ההכי טובים</v>
+        <v>מיכל גרינגליק – לוח זכרונות</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מיכל גרינגליק – לוח זכרונות</v>
+        <v>החצר האחורית – השקר יושב בראש השולחן</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%9b%d7%9c-%d7%92%d7%a8%d7%99%d7%a0%d7%92%d7%9c%d7%99%d7%a7-%d7%9c%d7%95%d7%97-%d7%96%d7%9b%d7%a8%d7%95%d7%a0%d7%95%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%94%d7%97%d7%a6%d7%a8-%d7%94%d7%90%d7%97%d7%95%d7%a8%d7%99%d7%aa-%d7%94%d7%a9%d7%a7%d7%a8-%d7%99%d7%95%d7%a9%d7%91-%d7%91%d7%a8%d7%90%d7%a9-%d7%94%d7%a9%d7%95%d7%9c%d7%97%d7%9f/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-17</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "לוח זכרונות" של מיכל גרינגליק מציג חוויה מאוד אישית של אבל בתוך מסגרת קולקטיבית של יום הזיכרון לחללי צה"ל. זה שיר שלא רק מתאר כאב – הוא  מתנהל בתוך הכאב, תוך ניסיון כושל (ומודע לעצמו) לעבד אותו דרך מוזיקה.</v>
+        <v>השיר, פרי עטו של יענקל'ה רוטבליט,  ובביצוע החצר האחורית  הוא לא רק שיר מחאה, אלא טקסט אלגורי צפוף, כמעט פיוטי־נבואי, שמבקש לזעזע יותר מאשר לשכנע. כאן כבר לא מדובר במחאה “ישירה”  אלא ביצירת עולם סמלי שלם. מבנה השיר חורג מאוד</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מיכל גרינגליק – לוח זכרונות</v>
+        <v>החצר האחורית – השקר יושב בראש השולחן</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>החצר האחורית – השקר יושב בראש השולחן</v>
+        <v>תום קינן – תפוח בדם</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%97%d7%a6%d7%a8-%d7%94%d7%90%d7%97%d7%95%d7%a8%d7%99%d7%aa-%d7%94%d7%a9%d7%a7%d7%a8-%d7%99%d7%95%d7%a9%d7%91-%d7%91%d7%a8%d7%90%d7%a9-%d7%94%d7%a9%d7%95%d7%9c%d7%97%d7%9f/</v>
+        <v>https://yosmusic.com/%d7%aa%d7%95%d7%9d-%d7%a7%d7%99%d7%a0%d7%9f-%d7%aa%d7%a4%d7%95%d7%97-%d7%91%d7%93%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר, פרי עטו של יענקל'ה רוטבליט,  ובביצוע החצר האחורית  הוא לא רק שיר מחאה, אלא טקסט אלגורי צפוף, כמעט פיוטי־נבואי, שמבקש לזעזע יותר מאשר לשכנע. כאן כבר לא מדובר במחאה “ישירה”  אלא ביצירת עולם סמלי שלם. מבנה השיר חורג מאוד</v>
+        <v>השיר "תפוח בדם" של תום קינן פועל על קצה עדין מאוד של שירת אבל – לא זעקה, אלא כמעט לחישה. הוא מצטרף באופן טבעי למרחב הרגשי של יום הזיכרון לחללי צה"ל, אך בוחר דרך מינימליסטית ומאופקת במקום דרמה גלויה. הציר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>החצר האחורית – השקר יושב בראש השולחן</v>
+        <v>תום קינן – תפוח בדם</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תום קינן – תפוח בדם</v>
+        <v>ליאור נרקיס – את משגעת אותי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-18</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%aa%d7%95%d7%9d-%d7%a7%d7%99%d7%a0%d7%9f-%d7%aa%d7%a4%d7%95%d7%97-%d7%91%d7%93%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%9c%d7%99%d7%90%d7%95%d7%a8-%d7%a0%d7%a8%d7%a7%d7%99%d7%a1-%d7%90%d7%aa-%d7%9e%d7%a9%d7%92%d7%a2%d7%aa-%d7%90%d7%95%d7%aa%d7%99/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-18</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "תפוח בדם" של תום קינן פועל על קצה עדין מאוד של שירת אבל – לא זעקה, אלא כמעט לחישה. הוא מצטרף באופן טבעי למרחב הרגשי של יום הזיכרון לחללי צה"ל, אך בוחר דרך מינימליסטית ומאופקת במקום דרמה גלויה. הציר</v>
+        <v>המוטו של ליאור נרקיס מאפיין את זמרי הז'אנר: שמחה כניתוק מהמציאות. "את משגעת אותי" הוא שיר שנבנה קודם כול כדי לעבוד על רחבת הריקודים באוריינטציה חפלאית. מציאות: הפסקת מלחמה, אובדן, ימי זיכרון  השיר: אהבה קלילה, תשוקה, חגיגה.  זו בחירה מחושבת</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תום קינן – תפוח בדם</v>
+        <v>ליאור נרקיס – את משגעת אותי</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ליאור נרקיס – את משגעת אותי</v>
+        <v>עברי לידר – מכתב מהעורף</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9c%d7%99%d7%90%d7%95%d7%a8-%d7%a0%d7%a8%d7%a7%d7%99%d7%a1-%d7%90%d7%aa-%d7%9e%d7%a9%d7%92%d7%a2%d7%aa-%d7%90%d7%95%d7%aa%d7%99/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%91%d7%a8%d7%99-%d7%9c%d7%99%d7%93%d7%a8-%d7%9e%d7%9b%d7%aa%d7%91-%d7%9e%d7%94%d7%a2%d7%95%d7%a8%d7%a3/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>המוטו של ליאור נרקיס מאפיין את זמרי הז'אנר: שמחה כניתוק מהמציאות. "את משגעת אותי" הוא שיר שנבנה קודם כול כדי לעבוד על רחבת הריקודים באוריינטציה חפלאית. מציאות: הפסקת מלחמה, אובדן, ימי זיכרון  השיר: אהבה קלילה, תשוקה, חגיגה.  זו בחירה מחושבת</v>
+        <v>השיר "מכתב מהעורף" של עברי לידר עולה על הנתיב המרכזי ל“נסיעה של שבת בצהריים”, ועם כל הזרימה והנגישות הוא מתמודד עם מצב מורכב – הפער המוסרי והרגשי העמוק בין העורף לחזית. מבנה השיר – זרם תודעה בתנועה – אין התחלה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ליאור נרקיס – את משגעת אותי</v>
+        <v>עברי לידר – מכתב מהעורף</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עברי לידר – מכתב מהעורף</v>
+        <v>משי קלינשטיין – הבלדה על חדווה ושמוליק</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-19</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%91%d7%a8%d7%99-%d7%9c%d7%99%d7%93%d7%a8-%d7%9e%d7%9b%d7%aa%d7%91-%d7%9e%d7%94%d7%a2%d7%95%d7%a8%d7%a3/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%a9%d7%99-%d7%a7%d7%9c%d7%99%d7%a0%d7%a9%d7%98%d7%99%d7%99%d7%9f-%d7%94%d7%91%d7%9c%d7%93%d7%94-%d7%a2%d7%9c-%d7%97%d7%93%d7%95%d7%95%d7%94-%d7%95%d7%a9%d7%9e%d7%95%d7%9c%d7%99%d7%a7/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-19</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "מכתב מהעורף" של עברי לידר עולה על הנתיב המרכזי ל“נסיעה של שבת בצהריים”, ועם כל הזרימה והנגישות הוא מתמודד עם מצב מורכב – הפער המוסרי והרגשי העמוק בין העורף לחזית. מבנה השיר – זרם תודעה בתנועה – אין התחלה</v>
+        <v>הקאבר של משי קלינשטיין ל“הבלדה לחדווה ושלומיק”  שיר שהלחין יאיר רוזנבלום  במסגרת המחזמר "מיקה שלי" הוא מהלך מעניין של “העתקה רגשית”: לקחת שיר שמושר בדרך כלל מתוך פשטות ישירה, ולהלביש עליו אסתטיקה כמעט חלומית, ריחופית ומעובדת. אבל לא כל מה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עברי לידר – מכתב מהעורף</v>
+        <v>משי קלינשטיין – הבלדה על חדווה ושמוליק</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>משי קלינשטיין – הבלדה על חדווה ושמוליק</v>
+        <v>נועם ראש – איטליה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%a9%d7%99-%d7%a7%d7%9c%d7%99%d7%a0%d7%a9%d7%98%d7%99%d7%99%d7%9f-%d7%94%d7%91%d7%9c%d7%93%d7%94-%d7%a2%d7%9c-%d7%97%d7%93%d7%95%d7%95%d7%94-%d7%95%d7%a9%d7%9e%d7%95%d7%9c%d7%99%d7%a7/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%9d-%d7%a8%d7%90%d7%a9-%d7%90%d7%99%d7%98%d7%9c%d7%99%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הקאבר של משי קלינשטיין ל“הבלדה לחדווה ושלומיק”  שיר שהלחין יאיר רוזנבלום  במסגרת המחזמר "מיקה שלי" הוא מהלך מעניין של “העתקה רגשית”: לקחת שיר שמושר בדרך כלל מתוך פשטות ישירה, ולהלביש עליו אסתטיקה כמעט חלומית, ריחופית ומעובדת. אבל לא כל מה</v>
+        <v>נועם ראש שרה שיר זיכרון אינטימי שמוותר מראש על דרמה גדולה, בוחרת באסתטיקה של ריחוק, עמעום והחמצה. זה לא שיר על אהבה בזמן אמת, אלא על הבנה מאוחרת מדי של מה שהיה. המוזיקה איטית, עיבוד אקוסטי לכלי מיתר, שירה כמעט</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>משי קלינשטיין – הבלדה על חדווה ושמוליק</v>
+        <v>נועם ראש – איטליה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נועם ראש – איטליה</v>
+        <v>מדונה I Feel So Free</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%9d-%d7%a8%d7%90%d7%a9-%d7%90%d7%99%d7%98%d7%9c%d7%99%d7%94/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%93%d7%95%d7%a0%d7%94-i-feel-so-free/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>נועם ראש שרה שיר זיכרון אינטימי שמוותר מראש על דרמה גדולה, בוחרת באסתטיקה של ריחוק, עמעום והחמצה. זה לא שיר על אהבה בזמן אמת, אלא על הבנה מאוחרת מדי של מה שהיה. המוזיקה איטית, עיבוד אקוסטי לכלי מיתר, שירה כמעט</v>
+        <v>“I Feel So Free” הוא קטע דאנס דוחף ואנרגטי שמשתלב באוריינטציה של האלבום Confessions on a Dance Floor, ומהדהד את הצליל של “Future Lovers” מתקופת האלקטרו־פופ של מדונה ב־2005. הכינוי “מלכת הפופ” עדיין מוצמד באופן קבוע לשמה של מדונה, אבל</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נועם ראש – איטליה</v>
+        <v>מדונה I Feel So Free</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מדונה I Feel So Free</v>
+        <v>הראל סקעת – נקום</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-21</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%93%d7%95%d7%a0%d7%94-i-feel-so-free/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a8%d7%90%d7%9c-%d7%a1%d7%a7%d7%a2%d7%aa-%d7%a0%d7%a7%d7%95%d7%9d/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-21</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“I Feel So Free” הוא קטע דאנס דוחף ואנרגטי שמשתלב באוריינטציה של האלבום Confessions on a Dance Floor, ומהדהד את הצליל של “Future Lovers” מתקופת האלקטרו־פופ של מדונה ב־2005. הכינוי “מלכת הפופ” עדיין מוצמד באופן קבוע לשמה של מדונה, אבל</v>
+        <v>השיר"נקום” של הראל סקעת יושב על התפר שבין אבל פרטי לטראומה קולקטיבית. "מדינה של מדבקות על ספסלים / צמידים על הידיים / וחור בלב” – בפתח השיר תיאורים יומיומיים מאוד ישראליים – “מדבקות” ו“צמידים” הם סמלים של זיכרון ציבורי, כמעט</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מדונה I Feel So Free</v>
+        <v>הראל סקעת – נקום</v>
       </c>
     </row>
   </sheetData>
